--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="341">
   <si>
     <t>TileID</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>County</t>
-  </si>
-  <si>
-    <t>Region</t>
   </si>
   <si>
     <t>Delaware County</t>
@@ -1468,37 +1465,37 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1509,37 +1506,37 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1550,37 +1547,37 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1591,529 +1588,493 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="2:15">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -2121,37 +2082,37 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -2159,37 +2120,37 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -2197,37 +2158,37 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -2235,37 +2196,37 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J21" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -2273,37 +2234,37 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -2311,37 +2272,37 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" spans="2:15">
@@ -2349,37 +2310,37 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -2387,37 +2348,37 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J25" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -2425,37 +2386,37 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -2463,37 +2424,37 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K27" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -2501,37 +2462,37 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -2539,37 +2500,37 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K29" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -2577,37 +2538,37 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -2615,37 +2576,37 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="2:15">
@@ -2653,37 +2614,37 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -2691,37 +2652,37 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K33" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -2729,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" spans="2:15">
@@ -2767,37 +2728,37 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -2805,37 +2766,37 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -2843,37 +2804,37 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J37" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K37" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -2881,37 +2842,37 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I38" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K38" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -2919,37 +2880,37 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -2957,37 +2918,37 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -2995,37 +2956,37 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3033,37 +2994,37 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3071,37 +3032,37 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J43" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3109,37 +3070,37 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3147,37 +3108,37 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I45" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J45" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3185,37 +3146,37 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I46" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J46" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3223,1291 +3184,1390 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K47" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="2:15">
       <c r="B48" t="s">
         <v>15</v>
       </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J48" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="2:15">
       <c r="B49" t="s">
         <v>15</v>
       </c>
+      <c r="C49" t="s">
+        <v>17</v>
+      </c>
       <c r="D49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I49" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K49" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="2:15">
       <c r="B50" t="s">
         <v>15</v>
       </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K50" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="2:15">
       <c r="B51" t="s">
         <v>15</v>
       </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I51" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K51" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="2:15">
       <c r="B52" t="s">
         <v>15</v>
       </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I52" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" spans="2:15">
       <c r="B53" t="s">
         <v>15</v>
       </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="2:15">
       <c r="B54" t="s">
         <v>15</v>
       </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K54" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="55" spans="2:15">
       <c r="B55" t="s">
         <v>15</v>
       </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
       <c r="D55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I55" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J55" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="2:15">
       <c r="B56" t="s">
         <v>15</v>
       </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J56" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K56" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="2:15">
       <c r="B57" t="s">
         <v>15</v>
       </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
       <c r="D57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G57" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I57" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="2:15">
       <c r="B58" t="s">
         <v>15</v>
       </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
       <c r="D58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I58" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J58" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K58" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59" spans="2:15">
       <c r="B59" t="s">
         <v>15</v>
       </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I59" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J59" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="60" spans="2:15">
       <c r="B60" t="s">
         <v>15</v>
       </c>
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J60" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K60" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="2:15">
       <c r="B61" t="s">
         <v>15</v>
       </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J61" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="2:15">
       <c r="B62" t="s">
         <v>15</v>
       </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I62" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J62" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K62" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63" spans="2:15">
       <c r="B63" t="s">
         <v>15</v>
       </c>
+      <c r="C63" t="s">
+        <v>17</v>
+      </c>
       <c r="D63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K63" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="2:15">
       <c r="B64" t="s">
         <v>15</v>
       </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I64" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="2:15">
       <c r="B65" t="s">
         <v>15</v>
       </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J65" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K65" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="2:15">
       <c r="B66" t="s">
         <v>15</v>
       </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I66" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J66" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K66" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="2:15">
       <c r="B67" t="s">
         <v>15</v>
       </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J67" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K67" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="2:15">
       <c r="B68" t="s">
         <v>15</v>
       </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K68" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="2:15">
       <c r="B69" t="s">
         <v>15</v>
       </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J69" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K69" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="2:15">
       <c r="B70" t="s">
         <v>15</v>
       </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J70" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="2:15">
       <c r="B71" t="s">
         <v>15</v>
       </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K71" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="2:15">
       <c r="B72" t="s">
         <v>15</v>
       </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I72" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J72" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K72" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="2:15">
       <c r="B73" t="s">
         <v>15</v>
       </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E73" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I73" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J73" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K73" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="2:15">
       <c r="B74" t="s">
         <v>15</v>
       </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="2:15">
       <c r="B75" t="s">
         <v>15</v>
       </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I75" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J75" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K75" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="2:15">
       <c r="B76" t="s">
         <v>15</v>
       </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I76" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K76" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="2:15">
       <c r="B77" t="s">
         <v>15</v>
       </c>
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
       <c r="D77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J77" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K77" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="2:15">
       <c r="B78" t="s">
         <v>15</v>
       </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I78" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J78" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K78" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="2:15">
       <c r="B79" t="s">
         <v>15</v>
       </c>
+      <c r="C79" t="s">
+        <v>17</v>
+      </c>
       <c r="D79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J79" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K79" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="2:15">
       <c r="B80" t="s">
         <v>15</v>
       </c>
+      <c r="C80" t="s">
+        <v>17</v>
+      </c>
       <c r="D80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G80" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I80" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J80" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="2:15">
@@ -4518,37 +4578,37 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I81" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K81" t="s">
+        <v>259</v>
+      </c>
+      <c r="M81" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="M81" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="N81" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="2:15">
@@ -4559,37 +4619,37 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J82" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K82" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="2:15">
@@ -4600,37 +4660,37 @@
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F83" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G83" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I83" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="2:15">
@@ -4641,529 +4701,493 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G84" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I84" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K84" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="2:15">
       <c r="B85" t="s">
         <v>16</v>
       </c>
-      <c r="C85" t="s">
-        <v>17</v>
-      </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G85" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J85" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K85" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="2:15">
       <c r="B86" t="s">
         <v>16</v>
       </c>
-      <c r="C86" t="s">
-        <v>17</v>
-      </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I86" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J86" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K86" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="2:15">
       <c r="B87" t="s">
         <v>16</v>
       </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J87" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K87" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" spans="2:15">
       <c r="B88" t="s">
         <v>16</v>
       </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
       <c r="D88" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E88" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K88" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" spans="2:15">
       <c r="B89" t="s">
         <v>16</v>
       </c>
-      <c r="C89" t="s">
-        <v>17</v>
-      </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F89" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G89" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I89" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="2:15">
       <c r="B90" t="s">
         <v>16</v>
       </c>
-      <c r="C90" t="s">
-        <v>17</v>
-      </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F90" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G90" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="91" spans="2:15">
       <c r="B91" t="s">
         <v>16</v>
       </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E91" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I91" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="92" spans="2:15">
       <c r="B92" t="s">
         <v>16</v>
       </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I92" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J92" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K92" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93" spans="2:15">
       <c r="B93" t="s">
         <v>16</v>
       </c>
-      <c r="C93" t="s">
-        <v>17</v>
-      </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I93" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J93" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K93" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="94" spans="2:15">
       <c r="B94" t="s">
         <v>16</v>
       </c>
-      <c r="C94" t="s">
-        <v>17</v>
-      </c>
       <c r="D94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I94" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J94" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K94" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="95" spans="2:15">
       <c r="B95" t="s">
         <v>16</v>
       </c>
-      <c r="C95" t="s">
-        <v>17</v>
-      </c>
       <c r="D95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I95" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J95" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K95" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="96" spans="2:15">
       <c r="B96" t="s">
         <v>16</v>
       </c>
-      <c r="C96" t="s">
-        <v>18</v>
-      </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I96" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J96" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K96" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="97" spans="2:15">
@@ -5171,37 +5195,37 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I97" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J97" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K97" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="98" spans="2:15">
@@ -5209,37 +5233,37 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I98" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K98" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="99" spans="2:15">
@@ -5247,37 +5271,37 @@
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I99" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J99" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K99" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="100" spans="2:15">
@@ -5285,37 +5309,37 @@
         <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I100" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J100" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K100" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="101" spans="2:15">
@@ -5323,37 +5347,37 @@
         <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E101" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I101" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="102" spans="2:15">
@@ -5361,37 +5385,37 @@
         <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E102" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I102" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J102" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K102" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="103" spans="2:15">
@@ -5399,37 +5423,37 @@
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I103" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J103" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K103" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="104" spans="2:15">
@@ -5437,37 +5461,37 @@
         <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I104" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J104" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K104" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="105" spans="2:15">
@@ -5475,37 +5499,37 @@
         <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E105" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F105" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G105" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I105" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J105" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K105" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="106" spans="2:15">
@@ -5513,37 +5537,37 @@
         <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E106" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F106" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G106" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I106" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J106" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K106" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="107" spans="2:15">
@@ -5551,37 +5575,37 @@
         <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F107" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G107" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J107" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="108" spans="2:15">
@@ -5589,37 +5613,37 @@
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E108" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I108" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J108" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K108" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="109" spans="2:15">
@@ -5627,37 +5651,37 @@
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E109" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F109" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G109" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I109" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J109" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K109" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="110" spans="2:15">
@@ -5665,37 +5689,37 @@
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E110" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F110" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G110" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I110" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K110" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="2:15">
@@ -5703,37 +5727,37 @@
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E111" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G111" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I111" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J111" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K111" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112" spans="2:15">
@@ -5741,37 +5765,37 @@
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E112" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F112" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G112" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I112" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J112" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K112" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="113" spans="2:15">
@@ -5779,37 +5803,37 @@
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F113" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G113" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I113" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J113" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K113" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="114" spans="2:15">
@@ -5817,37 +5841,37 @@
         <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E114" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I114" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J114" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K114" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="2:15">
@@ -5855,37 +5879,37 @@
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E115" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F115" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G115" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I115" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J115" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K115" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116" spans="2:15">
@@ -5893,37 +5917,37 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I116" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J116" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K116" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="2:15">
@@ -5931,37 +5955,37 @@
         <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E117" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F117" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G117" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I117" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J117" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K117" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="2:15">
@@ -5969,37 +5993,37 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E118" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F118" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G118" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I118" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J118" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K118" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="119" spans="2:15">
@@ -6007,37 +6031,37 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E119" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F119" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G119" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I119" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J119" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K119" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="120" spans="2:15">
@@ -6045,37 +6069,37 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G120" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I120" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J120" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="121" spans="2:15">
@@ -6083,37 +6107,37 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F121" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G121" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I121" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J121" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K121" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="122" spans="2:15">
@@ -6121,37 +6145,37 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E122" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F122" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G122" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I122" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J122" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K122" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" spans="2:15">
@@ -6159,37 +6183,37 @@
         <v>16</v>
       </c>
       <c r="D123" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E123" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F123" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G123" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I123" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J123" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K123" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="124" spans="2:15">
@@ -6197,37 +6221,37 @@
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E124" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G124" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I124" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J124" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K124" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -6235,37 +6259,37 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E125" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F125" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G125" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I125" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J125" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K125" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="126" spans="2:15">
@@ -6273,1291 +6297,1390 @@
         <v>16</v>
       </c>
       <c r="D126" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E126" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F126" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G126" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I126" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J126" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K126" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="127" spans="2:15">
       <c r="B127" t="s">
         <v>16</v>
       </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
       <c r="D127" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E127" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I127" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J127" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K127" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="128" spans="2:15">
       <c r="B128" t="s">
         <v>16</v>
       </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
       <c r="D128" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E128" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G128" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I128" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J128" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K128" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="129" spans="2:15">
       <c r="B129" t="s">
         <v>16</v>
       </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
       <c r="D129" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E129" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F129" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G129" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I129" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J129" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K129" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="130" spans="2:15">
       <c r="B130" t="s">
         <v>16</v>
       </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
       <c r="D130" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E130" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F130" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G130" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I130" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J130" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K130" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="131" spans="2:15">
       <c r="B131" t="s">
         <v>16</v>
       </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
       <c r="D131" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E131" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F131" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G131" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I131" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J131" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K131" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="132" spans="2:15">
       <c r="B132" t="s">
         <v>16</v>
       </c>
+      <c r="C132" t="s">
+        <v>17</v>
+      </c>
       <c r="D132" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E132" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F132" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G132" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J132" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K132" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="133" spans="2:15">
       <c r="B133" t="s">
         <v>16</v>
       </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
       <c r="D133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E133" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F133" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G133" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I133" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J133" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K133" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="134" spans="2:15">
       <c r="B134" t="s">
         <v>16</v>
       </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
       <c r="D134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E134" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F134" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G134" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I134" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J134" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K134" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="135" spans="2:15">
       <c r="B135" t="s">
         <v>16</v>
       </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
       <c r="D135" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E135" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F135" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G135" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I135" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J135" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K135" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="136" spans="2:15">
       <c r="B136" t="s">
         <v>16</v>
       </c>
+      <c r="C136" t="s">
+        <v>17</v>
+      </c>
       <c r="D136" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E136" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F136" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G136" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I136" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J136" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K136" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="137" spans="2:15">
       <c r="B137" t="s">
         <v>16</v>
       </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
       <c r="D137" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E137" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F137" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G137" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I137" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J137" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K137" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="138" spans="2:15">
       <c r="B138" t="s">
         <v>16</v>
       </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
       <c r="D138" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E138" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F138" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G138" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I138" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J138" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="139" spans="2:15">
       <c r="B139" t="s">
         <v>16</v>
       </c>
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
       <c r="D139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E139" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F139" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G139" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I139" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J139" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K139" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="140" spans="2:15">
       <c r="B140" t="s">
         <v>16</v>
       </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
       <c r="D140" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E140" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F140" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G140" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I140" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J140" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="141" spans="2:15">
       <c r="B141" t="s">
         <v>16</v>
       </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
       <c r="D141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E141" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F141" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G141" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I141" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J141" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K141" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="142" spans="2:15">
       <c r="B142" t="s">
         <v>16</v>
       </c>
+      <c r="C142" t="s">
+        <v>17</v>
+      </c>
       <c r="D142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E142" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F142" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G142" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I142" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J142" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K142" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="143" spans="2:15">
       <c r="B143" t="s">
         <v>16</v>
       </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
       <c r="D143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E143" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F143" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G143" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I143" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J143" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K143" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="144" spans="2:15">
       <c r="B144" t="s">
         <v>16</v>
       </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
       <c r="D144" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E144" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F144" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G144" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I144" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J144" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="145" spans="2:15">
       <c r="B145" t="s">
         <v>16</v>
       </c>
+      <c r="C145" t="s">
+        <v>17</v>
+      </c>
       <c r="D145" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E145" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F145" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G145" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I145" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J145" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K145" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="2:15">
       <c r="B146" t="s">
         <v>16</v>
       </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
       <c r="D146" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E146" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F146" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G146" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I146" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J146" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K146" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="2:15">
       <c r="B147" t="s">
         <v>16</v>
       </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
       <c r="D147" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E147" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F147" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G147" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I147" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J147" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K147" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="2:15">
       <c r="B148" t="s">
         <v>16</v>
       </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
       <c r="D148" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E148" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F148" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G148" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I148" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J148" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K148" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="149" spans="2:15">
       <c r="B149" t="s">
         <v>16</v>
       </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
       <c r="D149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E149" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F149" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G149" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I149" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J149" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K149" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="2:15">
       <c r="B150" t="s">
         <v>16</v>
       </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
       <c r="D150" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E150" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F150" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G150" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I150" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J150" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K150" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="151" spans="2:15">
       <c r="B151" t="s">
         <v>16</v>
       </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
       <c r="D151" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E151" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F151" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G151" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I151" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J151" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K151" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="2:15">
       <c r="B152" t="s">
         <v>16</v>
       </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
       <c r="D152" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E152" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F152" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G152" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I152" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J152" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K152" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O152" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="153" spans="2:15">
       <c r="B153" t="s">
         <v>16</v>
       </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
       <c r="D153" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E153" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F153" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G153" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I153" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J153" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K153" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="154" spans="2:15">
       <c r="B154" t="s">
         <v>16</v>
       </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
       <c r="D154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F154" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G154" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I154" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J154" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="155" spans="2:15">
       <c r="B155" t="s">
         <v>16</v>
       </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
       <c r="D155" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E155" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F155" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G155" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I155" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J155" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K155" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="156" spans="2:15">
       <c r="B156" t="s">
         <v>16</v>
       </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
       <c r="D156" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E156" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F156" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G156" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I156" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J156" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K156" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="2:15">
       <c r="B157" t="s">
         <v>16</v>
       </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
       <c r="D157" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E157" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F157" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G157" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I157" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J157" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="158" spans="2:15">
       <c r="B158" t="s">
         <v>16</v>
       </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
       <c r="D158" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E158" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F158" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G158" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I158" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J158" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O158" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159" spans="2:15">
       <c r="B159" t="s">
         <v>16</v>
       </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
       <c r="D159" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E159" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F159" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G159" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I159" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J159" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K159" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O159" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="346">
   <si>
     <t>TileID</t>
   </si>
@@ -70,6 +70,9 @@
     <t>County</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>Delaware County</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
     <t>Urbancrest</t>
   </si>
   <si>
+    <t>Westerville</t>
+  </si>
+  <si>
     <t>West Jefferson</t>
   </si>
   <si>
@@ -541,6 +547,9 @@
     <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/facilities-Urbancrest-M100000US3979100.svg</t>
   </si>
   <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/facilities-Westerville-M100000US3983342.svg</t>
+  </si>
+  <si>
     <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/facilities-WestJefferson-M100000US3983580.svg</t>
   </si>
   <si>
@@ -778,6 +787,9 @@
     <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/capacity-Urbancrest-M100000US3979100.svg</t>
   </si>
   <si>
+    <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/capacity-Westerville-M100000US3983342.svg</t>
+  </si>
+  <si>
     <t>https://raw.githubusercontent.com/morpc-insights/renewenergy-der/refs/heads/main/output_data/charts/capacity-WestJefferson-M100000US3983580.svg</t>
   </si>
   <si>
@@ -1022,6 +1034,9 @@
   </si>
   <si>
     <t>https://www.arcgis.com/apps/dashboards/3f2b48c930294cfda824567333f001fd#geoid=M100000US3979100</t>
+  </si>
+  <si>
+    <t>https://www.arcgis.com/apps/dashboards/3f2b48c930294cfda824567333f001fd#geoid=M100000US3983342</t>
   </si>
   <si>
     <t>https://www.arcgis.com/apps/dashboards/3f2b48c930294cfda824567333f001fd#geoid=M100000US3983580</t>
@@ -1407,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O159"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1465,37 +1480,37 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1506,37 +1521,37 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -1547,37 +1562,37 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1588,493 +1603,529 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J5" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6" t="s">
         <v>15</v>
       </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" t="s">
         <v>15</v>
       </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I7" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8" t="s">
         <v>15</v>
       </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I8" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K8" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
         <v>15</v>
       </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I9" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J9" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K9" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
         <v>15</v>
       </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
         <v>15</v>
       </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I11" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K11" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
         <v>15</v>
       </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I12" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K12" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
         <v>15</v>
       </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J13" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K13" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14" t="s">
         <v>15</v>
       </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I14" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K14" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15" t="s">
         <v>15</v>
       </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I15" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J15" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K15" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="B16" t="s">
         <v>15</v>
       </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J16" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K16" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="2:15">
       <c r="B17" t="s">
         <v>15</v>
       </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I17" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J17" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K17" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -2082,37 +2133,37 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J18" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K18" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -2120,37 +2171,37 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I19" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J19" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K19" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -2158,37 +2209,37 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I20" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J20" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K20" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -2196,37 +2247,37 @@
         <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I21" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J21" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K21" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -2234,37 +2285,37 @@
         <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I22" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J22" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K22" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -2272,37 +2323,37 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I23" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J23" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K23" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="2:15">
@@ -2310,37 +2361,37 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I24" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K24" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -2348,37 +2399,37 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J25" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K25" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -2386,37 +2437,37 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I26" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J26" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K26" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -2424,37 +2475,37 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K27" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -2462,37 +2513,37 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I28" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J28" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K28" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -2500,37 +2551,37 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I29" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J29" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K29" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -2538,37 +2589,37 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I30" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J30" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K30" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -2576,37 +2627,37 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I31" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J31" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K31" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="2:15">
@@ -2614,37 +2665,37 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I32" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J32" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K32" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -2652,37 +2703,37 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I33" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J33" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K33" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -2690,37 +2741,37 @@
         <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I34" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J34" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="2:15">
@@ -2728,37 +2779,37 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I35" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J35" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K35" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -2766,37 +2817,37 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I36" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J36" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K36" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -2804,37 +2855,37 @@
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I37" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J37" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K37" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -2842,37 +2893,37 @@
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I38" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J38" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -2880,37 +2931,37 @@
         <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J39" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -2918,37 +2969,37 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I40" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J40" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K40" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -2956,37 +3007,37 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J41" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K41" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -2994,37 +3045,37 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I42" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J42" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K42" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3032,37 +3083,37 @@
         <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I43" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J43" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K43" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3070,37 +3121,37 @@
         <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I44" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J44" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K44" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3108,37 +3159,37 @@
         <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I45" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J45" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K45" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3146,37 +3197,37 @@
         <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G46" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I46" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J46" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K46" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3184,1431 +3235,1329 @@
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F47" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I47" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J47" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K47" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" spans="2:15">
       <c r="B48" t="s">
         <v>15</v>
       </c>
-      <c r="C48" t="s">
-        <v>17</v>
-      </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I48" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J48" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K48" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="2:15">
       <c r="B49" t="s">
         <v>15</v>
       </c>
-      <c r="C49" t="s">
-        <v>17</v>
-      </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I49" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J49" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K49" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="2:15">
       <c r="B50" t="s">
         <v>15</v>
       </c>
-      <c r="C50" t="s">
-        <v>17</v>
-      </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I50" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J50" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K50" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="2:15">
       <c r="B51" t="s">
         <v>15</v>
       </c>
-      <c r="C51" t="s">
-        <v>17</v>
-      </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I51" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J51" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K51" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="2:15">
       <c r="B52" t="s">
         <v>15</v>
       </c>
-      <c r="C52" t="s">
-        <v>17</v>
-      </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I52" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J52" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K52" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="2:15">
       <c r="B53" t="s">
         <v>15</v>
       </c>
-      <c r="C53" t="s">
-        <v>17</v>
-      </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F53" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G53" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I53" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J53" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K53" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" spans="2:15">
       <c r="B54" t="s">
         <v>15</v>
       </c>
-      <c r="C54" t="s">
-        <v>17</v>
-      </c>
       <c r="D54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I54" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J54" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K54" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="2:15">
       <c r="B55" t="s">
         <v>15</v>
       </c>
-      <c r="C55" t="s">
-        <v>17</v>
-      </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E55" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F55" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G55" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I55" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J55" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="2:15">
       <c r="B56" t="s">
         <v>15</v>
       </c>
-      <c r="C56" t="s">
-        <v>17</v>
-      </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E56" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F56" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G56" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I56" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J56" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K56" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="2:15">
       <c r="B57" t="s">
         <v>15</v>
       </c>
-      <c r="C57" t="s">
-        <v>17</v>
-      </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F57" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G57" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I57" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J57" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K57" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="2:15">
       <c r="B58" t="s">
         <v>15</v>
       </c>
-      <c r="C58" t="s">
-        <v>17</v>
-      </c>
       <c r="D58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E58" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F58" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G58" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I58" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J58" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K58" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="2:15">
       <c r="B59" t="s">
         <v>15</v>
       </c>
-      <c r="C59" t="s">
-        <v>17</v>
-      </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E59" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F59" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G59" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I59" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J59" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K59" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="2:15">
       <c r="B60" t="s">
         <v>15</v>
       </c>
-      <c r="C60" t="s">
-        <v>17</v>
-      </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I60" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J60" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K60" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="2:15">
       <c r="B61" t="s">
         <v>15</v>
       </c>
-      <c r="C61" t="s">
-        <v>17</v>
-      </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E61" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I61" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J61" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K61" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62" spans="2:15">
       <c r="B62" t="s">
         <v>15</v>
       </c>
-      <c r="C62" t="s">
-        <v>17</v>
-      </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F62" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I62" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J62" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K62" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="2:15">
       <c r="B63" t="s">
         <v>15</v>
       </c>
-      <c r="C63" t="s">
-        <v>17</v>
-      </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F63" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G63" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I63" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J63" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="2:15">
       <c r="B64" t="s">
         <v>15</v>
       </c>
-      <c r="C64" t="s">
-        <v>17</v>
-      </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I64" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J64" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K64" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="2:15">
       <c r="B65" t="s">
         <v>15</v>
       </c>
-      <c r="C65" t="s">
-        <v>17</v>
-      </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E65" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I65" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J65" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K65" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="2:15">
       <c r="B66" t="s">
         <v>15</v>
       </c>
-      <c r="C66" t="s">
-        <v>17</v>
-      </c>
       <c r="D66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F66" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G66" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I66" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J66" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="2:15">
       <c r="B67" t="s">
         <v>15</v>
       </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E67" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F67" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G67" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I67" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J67" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K67" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="2:15">
       <c r="B68" t="s">
         <v>15</v>
       </c>
-      <c r="C68" t="s">
-        <v>17</v>
-      </c>
       <c r="D68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F68" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G68" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I68" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J68" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K68" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="2:15">
       <c r="B69" t="s">
         <v>15</v>
       </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F69" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G69" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I69" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J69" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K69" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="2:15">
       <c r="B70" t="s">
         <v>15</v>
       </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
       <c r="D70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E70" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I70" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J70" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K70" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="2:15">
       <c r="B71" t="s">
         <v>15</v>
       </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
       <c r="D71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F71" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G71" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I71" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J71" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K71" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" spans="2:15">
       <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
       <c r="D72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E72" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G72" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I72" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J72" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K72" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="73" spans="2:15">
       <c r="B73" t="s">
         <v>15</v>
       </c>
-      <c r="C73" t="s">
-        <v>17</v>
-      </c>
       <c r="D73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F73" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G73" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I73" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J73" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="2:15">
       <c r="B74" t="s">
         <v>15</v>
       </c>
-      <c r="C74" t="s">
-        <v>17</v>
-      </c>
       <c r="D74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I74" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="2:15">
       <c r="B75" t="s">
         <v>15</v>
       </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
       <c r="D75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F75" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G75" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I75" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J75" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K75" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="2:15">
       <c r="B76" t="s">
         <v>15</v>
       </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
       <c r="D76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I76" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J76" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="2:15">
       <c r="B77" t="s">
         <v>15</v>
       </c>
-      <c r="C77" t="s">
-        <v>17</v>
-      </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E77" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F77" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G77" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I77" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J77" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K77" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="2:15">
       <c r="B78" t="s">
         <v>15</v>
       </c>
-      <c r="C78" t="s">
-        <v>17</v>
-      </c>
       <c r="D78" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F78" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G78" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I78" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J78" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K78" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="2:15">
       <c r="B79" t="s">
         <v>15</v>
       </c>
-      <c r="C79" t="s">
-        <v>17</v>
-      </c>
       <c r="D79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F79" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G79" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I79" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J79" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K79" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="2:15">
       <c r="B80" t="s">
         <v>15</v>
       </c>
-      <c r="C80" t="s">
-        <v>17</v>
-      </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E80" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F80" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G80" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I80" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J80" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K80" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="2:15">
       <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="E81" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F81" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G81" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I81" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J81" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K81" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="2:15">
@@ -4622,34 +4571,34 @@
         <v>19</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F82" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G82" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I82" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J82" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K82" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="2:15">
@@ -4663,34 +4612,34 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F83" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G83" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I83" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J83" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="2:15">
@@ -4704,528 +4653,567 @@
         <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F84" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G84" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I84" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J84" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="2:15">
       <c r="B85" t="s">
         <v>16</v>
       </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
       <c r="D85" t="s">
         <v>22</v>
       </c>
       <c r="E85" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F85" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G85" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I85" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J85" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="2:15">
       <c r="B86" t="s">
         <v>16</v>
       </c>
+      <c r="C86" t="s">
+        <v>17</v>
+      </c>
       <c r="D86" t="s">
         <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F86" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G86" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I86" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J86" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="2:15">
       <c r="B87" t="s">
         <v>16</v>
       </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
       <c r="D87" t="s">
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F87" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G87" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I87" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J87" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="2:15">
       <c r="B88" t="s">
         <v>16</v>
       </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
       <c r="D88" t="s">
         <v>25</v>
       </c>
       <c r="E88" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F88" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I88" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J88" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="2:15">
       <c r="B89" t="s">
         <v>16</v>
       </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
       <c r="D89" t="s">
         <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F89" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G89" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I89" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J89" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K89" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" spans="2:15">
       <c r="B90" t="s">
         <v>16</v>
       </c>
+      <c r="C90" t="s">
+        <v>17</v>
+      </c>
       <c r="D90" t="s">
         <v>27</v>
       </c>
       <c r="E90" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F90" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G90" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I90" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J90" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K90" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="2:15">
       <c r="B91" t="s">
         <v>16</v>
       </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
       <c r="D91" t="s">
         <v>28</v>
       </c>
       <c r="E91" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F91" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G91" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I91" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J91" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K91" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" spans="2:15">
       <c r="B92" t="s">
         <v>16</v>
       </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
       <c r="D92" t="s">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F92" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I92" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J92" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K92" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="93" spans="2:15">
       <c r="B93" t="s">
         <v>16</v>
       </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
       <c r="D93" t="s">
         <v>30</v>
       </c>
       <c r="E93" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G93" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I93" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J93" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K93" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="94" spans="2:15">
       <c r="B94" t="s">
         <v>16</v>
       </c>
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
       <c r="D94" t="s">
         <v>31</v>
       </c>
       <c r="E94" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F94" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G94" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I94" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J94" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K94" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="95" spans="2:15">
       <c r="B95" t="s">
         <v>16</v>
       </c>
+      <c r="C95" t="s">
+        <v>17</v>
+      </c>
       <c r="D95" t="s">
         <v>32</v>
       </c>
       <c r="E95" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F95" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G95" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I95" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J95" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K95" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="2:15">
       <c r="B96" t="s">
         <v>16</v>
       </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
       <c r="D96" t="s">
         <v>33</v>
       </c>
       <c r="E96" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F96" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G96" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I96" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J96" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K96" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="97" spans="2:15">
       <c r="B97" t="s">
         <v>16</v>
       </c>
+      <c r="C97" t="s">
+        <v>18</v>
+      </c>
       <c r="D97" t="s">
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G97" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I97" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J97" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K97" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="98" spans="2:15">
@@ -5236,34 +5224,34 @@
         <v>35</v>
       </c>
       <c r="E98" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F98" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G98" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I98" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J98" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K98" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="99" spans="2:15">
@@ -5274,34 +5262,34 @@
         <v>36</v>
       </c>
       <c r="E99" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F99" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I99" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J99" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K99" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="100" spans="2:15">
@@ -5312,34 +5300,34 @@
         <v>37</v>
       </c>
       <c r="E100" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F100" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G100" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I100" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J100" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K100" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="101" spans="2:15">
@@ -5350,34 +5338,34 @@
         <v>38</v>
       </c>
       <c r="E101" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F101" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G101" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I101" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J101" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K101" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="2:15">
@@ -5388,34 +5376,34 @@
         <v>39</v>
       </c>
       <c r="E102" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F102" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G102" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I102" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J102" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K102" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="103" spans="2:15">
@@ -5426,34 +5414,34 @@
         <v>40</v>
       </c>
       <c r="E103" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F103" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G103" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I103" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J103" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K103" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="2:15">
@@ -5464,34 +5452,34 @@
         <v>41</v>
       </c>
       <c r="E104" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F104" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G104" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I104" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J104" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K104" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="105" spans="2:15">
@@ -5502,34 +5490,34 @@
         <v>42</v>
       </c>
       <c r="E105" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F105" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G105" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I105" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J105" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K105" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106" spans="2:15">
@@ -5540,34 +5528,34 @@
         <v>43</v>
       </c>
       <c r="E106" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F106" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G106" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I106" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J106" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K106" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="107" spans="2:15">
@@ -5578,34 +5566,34 @@
         <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F107" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G107" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I107" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J107" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K107" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" spans="2:15">
@@ -5616,34 +5604,34 @@
         <v>45</v>
       </c>
       <c r="E108" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F108" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G108" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I108" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J108" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K108" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="109" spans="2:15">
@@ -5654,34 +5642,34 @@
         <v>46</v>
       </c>
       <c r="E109" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F109" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G109" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I109" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J109" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K109" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="110" spans="2:15">
@@ -5692,34 +5680,34 @@
         <v>47</v>
       </c>
       <c r="E110" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F110" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G110" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I110" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J110" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K110" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" spans="2:15">
@@ -5730,34 +5718,34 @@
         <v>48</v>
       </c>
       <c r="E111" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F111" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G111" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I111" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J111" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K111" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="2:15">
@@ -5768,34 +5756,34 @@
         <v>49</v>
       </c>
       <c r="E112" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F112" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G112" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I112" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J112" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K112" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="113" spans="2:15">
@@ -5806,34 +5794,34 @@
         <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F113" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G113" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I113" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J113" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K113" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="114" spans="2:15">
@@ -5844,34 +5832,34 @@
         <v>51</v>
       </c>
       <c r="E114" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F114" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G114" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I114" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J114" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K114" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="115" spans="2:15">
@@ -5882,34 +5870,34 @@
         <v>52</v>
       </c>
       <c r="E115" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F115" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G115" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I115" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J115" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K115" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="116" spans="2:15">
@@ -5920,34 +5908,34 @@
         <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F116" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G116" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I116" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J116" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K116" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="117" spans="2:15">
@@ -5958,34 +5946,34 @@
         <v>54</v>
       </c>
       <c r="E117" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F117" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G117" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I117" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J117" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K117" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118" spans="2:15">
@@ -5996,34 +5984,34 @@
         <v>55</v>
       </c>
       <c r="E118" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F118" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G118" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I118" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J118" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K118" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="119" spans="2:15">
@@ -6034,34 +6022,34 @@
         <v>56</v>
       </c>
       <c r="E119" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F119" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G119" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I119" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J119" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K119" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="2:15">
@@ -6072,34 +6060,34 @@
         <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F120" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G120" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I120" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J120" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K120" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="2:15">
@@ -6110,34 +6098,34 @@
         <v>58</v>
       </c>
       <c r="E121" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F121" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G121" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I121" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J121" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K121" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="122" spans="2:15">
@@ -6148,34 +6136,34 @@
         <v>59</v>
       </c>
       <c r="E122" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F122" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G122" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I122" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J122" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K122" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="123" spans="2:15">
@@ -6186,34 +6174,34 @@
         <v>60</v>
       </c>
       <c r="E123" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F123" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G123" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I123" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J123" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K123" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="124" spans="2:15">
@@ -6224,34 +6212,34 @@
         <v>61</v>
       </c>
       <c r="E124" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F124" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G124" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I124" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J124" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -6262,34 +6250,34 @@
         <v>62</v>
       </c>
       <c r="E125" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F125" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G125" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I125" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J125" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K125" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="126" spans="2:15">
@@ -6300,1387 +6288,1364 @@
         <v>63</v>
       </c>
       <c r="E126" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F126" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G126" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I126" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J126" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K126" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" spans="2:15">
       <c r="B127" t="s">
         <v>16</v>
       </c>
-      <c r="C127" t="s">
-        <v>17</v>
-      </c>
       <c r="D127" t="s">
         <v>64</v>
       </c>
       <c r="E127" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F127" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I127" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J127" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K127" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="128" spans="2:15">
       <c r="B128" t="s">
         <v>16</v>
       </c>
-      <c r="C128" t="s">
-        <v>17</v>
-      </c>
       <c r="D128" t="s">
         <v>65</v>
       </c>
       <c r="E128" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F128" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G128" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I128" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J128" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K128" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="2:15">
       <c r="B129" t="s">
         <v>16</v>
       </c>
-      <c r="C129" t="s">
-        <v>17</v>
-      </c>
       <c r="D129" t="s">
         <v>66</v>
       </c>
       <c r="E129" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F129" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G129" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I129" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J129" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K129" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="130" spans="2:15">
       <c r="B130" t="s">
         <v>16</v>
       </c>
-      <c r="C130" t="s">
-        <v>17</v>
-      </c>
       <c r="D130" t="s">
         <v>67</v>
       </c>
       <c r="E130" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F130" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G130" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I130" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J130" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K130" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="131" spans="2:15">
       <c r="B131" t="s">
         <v>16</v>
       </c>
-      <c r="C131" t="s">
-        <v>17</v>
-      </c>
       <c r="D131" t="s">
         <v>68</v>
       </c>
       <c r="E131" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F131" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G131" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I131" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J131" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K131" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="132" spans="2:15">
       <c r="B132" t="s">
         <v>16</v>
       </c>
-      <c r="C132" t="s">
-        <v>17</v>
-      </c>
       <c r="D132" t="s">
         <v>69</v>
       </c>
       <c r="E132" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F132" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G132" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I132" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J132" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K132" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="133" spans="2:15">
       <c r="B133" t="s">
         <v>16</v>
       </c>
-      <c r="C133" t="s">
-        <v>17</v>
-      </c>
       <c r="D133" t="s">
         <v>70</v>
       </c>
       <c r="E133" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F133" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G133" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I133" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J133" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K133" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="134" spans="2:15">
       <c r="B134" t="s">
         <v>16</v>
       </c>
-      <c r="C134" t="s">
-        <v>17</v>
-      </c>
       <c r="D134" t="s">
         <v>71</v>
       </c>
       <c r="E134" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F134" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G134" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I134" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J134" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K134" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="135" spans="2:15">
       <c r="B135" t="s">
         <v>16</v>
       </c>
-      <c r="C135" t="s">
-        <v>17</v>
-      </c>
       <c r="D135" t="s">
         <v>72</v>
       </c>
       <c r="E135" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F135" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G135" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I135" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J135" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K135" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="136" spans="2:15">
       <c r="B136" t="s">
         <v>16</v>
       </c>
-      <c r="C136" t="s">
-        <v>17</v>
-      </c>
       <c r="D136" t="s">
         <v>73</v>
       </c>
       <c r="E136" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F136" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G136" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I136" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J136" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="137" spans="2:15">
       <c r="B137" t="s">
         <v>16</v>
       </c>
-      <c r="C137" t="s">
-        <v>17</v>
-      </c>
       <c r="D137" t="s">
         <v>74</v>
       </c>
       <c r="E137" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F137" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G137" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I137" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J137" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="138" spans="2:15">
       <c r="B138" t="s">
         <v>16</v>
       </c>
-      <c r="C138" t="s">
-        <v>17</v>
-      </c>
       <c r="D138" t="s">
         <v>75</v>
       </c>
       <c r="E138" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F138" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G138" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I138" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J138" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K138" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="139" spans="2:15">
       <c r="B139" t="s">
         <v>16</v>
       </c>
-      <c r="C139" t="s">
-        <v>17</v>
-      </c>
       <c r="D139" t="s">
         <v>76</v>
       </c>
       <c r="E139" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F139" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G139" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I139" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J139" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K139" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="140" spans="2:15">
       <c r="B140" t="s">
         <v>16</v>
       </c>
-      <c r="C140" t="s">
-        <v>17</v>
-      </c>
       <c r="D140" t="s">
         <v>77</v>
       </c>
       <c r="E140" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F140" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G140" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I140" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J140" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K140" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="141" spans="2:15">
       <c r="B141" t="s">
         <v>16</v>
       </c>
-      <c r="C141" t="s">
-        <v>17</v>
-      </c>
       <c r="D141" t="s">
         <v>78</v>
       </c>
       <c r="E141" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F141" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G141" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I141" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J141" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K141" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="142" spans="2:15">
       <c r="B142" t="s">
         <v>16</v>
       </c>
-      <c r="C142" t="s">
-        <v>17</v>
-      </c>
       <c r="D142" t="s">
         <v>79</v>
       </c>
       <c r="E142" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F142" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G142" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I142" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J142" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K142" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="143" spans="2:15">
       <c r="B143" t="s">
         <v>16</v>
       </c>
-      <c r="C143" t="s">
-        <v>17</v>
-      </c>
       <c r="D143" t="s">
         <v>80</v>
       </c>
       <c r="E143" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F143" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G143" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I143" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J143" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K143" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="144" spans="2:15">
       <c r="B144" t="s">
         <v>16</v>
       </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
       <c r="D144" t="s">
         <v>81</v>
       </c>
       <c r="E144" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F144" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G144" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I144" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J144" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K144" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="145" spans="2:15">
       <c r="B145" t="s">
         <v>16</v>
       </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
       <c r="D145" t="s">
         <v>82</v>
       </c>
       <c r="E145" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F145" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G145" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I145" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J145" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K145" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="146" spans="2:15">
       <c r="B146" t="s">
         <v>16</v>
       </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
       <c r="D146" t="s">
         <v>83</v>
       </c>
       <c r="E146" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F146" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G146" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I146" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J146" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K146" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="2:15">
       <c r="B147" t="s">
         <v>16</v>
       </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
       <c r="D147" t="s">
         <v>84</v>
       </c>
       <c r="E147" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F147" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G147" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I147" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J147" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K147" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="148" spans="2:15">
       <c r="B148" t="s">
         <v>16</v>
       </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
       <c r="D148" t="s">
         <v>85</v>
       </c>
       <c r="E148" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F148" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G148" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I148" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J148" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="2:15">
       <c r="B149" t="s">
         <v>16</v>
       </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
       <c r="D149" t="s">
         <v>86</v>
       </c>
       <c r="E149" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F149" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G149" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I149" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J149" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K149" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="2:15">
       <c r="B150" t="s">
         <v>16</v>
       </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
       <c r="D150" t="s">
         <v>87</v>
       </c>
       <c r="E150" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F150" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G150" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I150" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J150" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K150" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O150" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="2:15">
       <c r="B151" t="s">
         <v>16</v>
       </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
       <c r="D151" t="s">
         <v>88</v>
       </c>
       <c r="E151" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F151" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G151" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I151" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J151" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K151" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="2:15">
       <c r="B152" t="s">
         <v>16</v>
       </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
       <c r="D152" t="s">
         <v>89</v>
       </c>
       <c r="E152" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F152" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G152" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I152" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J152" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K152" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O152" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="2:15">
       <c r="B153" t="s">
         <v>16</v>
       </c>
-      <c r="C153" t="s">
-        <v>17</v>
-      </c>
       <c r="D153" t="s">
         <v>90</v>
       </c>
       <c r="E153" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F153" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G153" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I153" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J153" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K153" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="154" spans="2:15">
       <c r="B154" t="s">
         <v>16</v>
       </c>
-      <c r="C154" t="s">
-        <v>17</v>
-      </c>
       <c r="D154" t="s">
         <v>91</v>
       </c>
       <c r="E154" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F154" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G154" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I154" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J154" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K154" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="155" spans="2:15">
       <c r="B155" t="s">
         <v>16</v>
       </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
       <c r="D155" t="s">
         <v>92</v>
       </c>
       <c r="E155" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F155" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G155" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I155" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J155" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K155" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="156" spans="2:15">
       <c r="B156" t="s">
         <v>16</v>
       </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
       <c r="D156" t="s">
         <v>93</v>
       </c>
       <c r="E156" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F156" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G156" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I156" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J156" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K156" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="157" spans="2:15">
       <c r="B157" t="s">
         <v>16</v>
       </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
       <c r="D157" t="s">
         <v>94</v>
       </c>
       <c r="E157" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F157" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G157" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I157" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J157" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K157" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="158" spans="2:15">
       <c r="B158" t="s">
         <v>16</v>
       </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
       <c r="D158" t="s">
         <v>95</v>
       </c>
       <c r="E158" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F158" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G158" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I158" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J158" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K158" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="O158" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="2:15">
       <c r="B159" t="s">
         <v>16</v>
       </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
       <c r="D159" t="s">
         <v>96</v>
       </c>
       <c r="E159" t="s">
+        <v>99</v>
+      </c>
+      <c r="F159" t="s">
+        <v>100</v>
+      </c>
+      <c r="G159" t="s">
+        <v>100</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I159" t="s">
+        <v>261</v>
+      </c>
+      <c r="J159" t="s">
+        <v>262</v>
+      </c>
+      <c r="K159" t="s">
+        <v>263</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="N159" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="O159" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="160" spans="2:15">
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="D160" t="s">
         <v>97</v>
       </c>
-      <c r="F159" t="s">
+      <c r="E160" t="s">
+        <v>99</v>
+      </c>
+      <c r="F160" t="s">
+        <v>100</v>
+      </c>
+      <c r="G160" t="s">
+        <v>100</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I160" t="s">
+        <v>261</v>
+      </c>
+      <c r="J160" t="s">
+        <v>262</v>
+      </c>
+      <c r="K160" t="s">
+        <v>263</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="N160" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="O160" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="161" spans="2:15">
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161" t="s">
         <v>98</v>
       </c>
-      <c r="G159" t="s">
-        <v>98</v>
-      </c>
-      <c r="H159" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I159" t="s">
-        <v>257</v>
-      </c>
-      <c r="J159" t="s">
-        <v>258</v>
-      </c>
-      <c r="K159" t="s">
-        <v>259</v>
-      </c>
-      <c r="M159" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="N159" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="O159" s="2" t="s">
-        <v>340</v>
+      <c r="E161" t="s">
+        <v>99</v>
+      </c>
+      <c r="F161" t="s">
+        <v>100</v>
+      </c>
+      <c r="G161" t="s">
+        <v>100</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I161" t="s">
+        <v>261</v>
+      </c>
+      <c r="J161" t="s">
+        <v>262</v>
+      </c>
+      <c r="K161" t="s">
+        <v>263</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N161" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="O161" s="2" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -7990,333 +7955,341 @@
     <hyperlink ref="N77" r:id="rId303"/>
     <hyperlink ref="O77" r:id="rId304"/>
     <hyperlink ref="H78" r:id="rId305"/>
-    <hyperlink ref="M78" r:id="rId306" location="geoid=M100000US3983580"/>
+    <hyperlink ref="M78" r:id="rId306" location="geoid=M100000US3983342"/>
     <hyperlink ref="N78" r:id="rId307"/>
     <hyperlink ref="O78" r:id="rId308"/>
     <hyperlink ref="H79" r:id="rId309"/>
-    <hyperlink ref="M79" r:id="rId310" location="geoid=M100000US3984742"/>
+    <hyperlink ref="M79" r:id="rId310" location="geoid=M100000US3983580"/>
     <hyperlink ref="N79" r:id="rId311"/>
     <hyperlink ref="O79" r:id="rId312"/>
     <hyperlink ref="H80" r:id="rId313"/>
-    <hyperlink ref="M80" r:id="rId314" location="geoid=M100000US3986604"/>
+    <hyperlink ref="M80" r:id="rId314" location="geoid=M100000US3984742"/>
     <hyperlink ref="N80" r:id="rId315"/>
     <hyperlink ref="O80" r:id="rId316"/>
     <hyperlink ref="H81" r:id="rId317"/>
-    <hyperlink ref="M81" r:id="rId318" location="geoid=0500000US39041"/>
+    <hyperlink ref="M81" r:id="rId318" location="geoid=M100000US3986604"/>
     <hyperlink ref="N81" r:id="rId319"/>
     <hyperlink ref="O81" r:id="rId320"/>
     <hyperlink ref="H82" r:id="rId321"/>
-    <hyperlink ref="M82" r:id="rId322" location="geoid=0500000US39045"/>
+    <hyperlink ref="M82" r:id="rId322" location="geoid=0500000US39041"/>
     <hyperlink ref="N82" r:id="rId323"/>
     <hyperlink ref="O82" r:id="rId324"/>
     <hyperlink ref="H83" r:id="rId325"/>
-    <hyperlink ref="M83" r:id="rId326" location="geoid=0500000US39047"/>
+    <hyperlink ref="M83" r:id="rId326" location="geoid=0500000US39045"/>
     <hyperlink ref="N83" r:id="rId327"/>
     <hyperlink ref="O83" r:id="rId328"/>
     <hyperlink ref="H84" r:id="rId329"/>
-    <hyperlink ref="M84" r:id="rId330" location="geoid=0500000US39049"/>
+    <hyperlink ref="M84" r:id="rId330" location="geoid=0500000US39047"/>
     <hyperlink ref="N84" r:id="rId331"/>
     <hyperlink ref="O84" r:id="rId332"/>
     <hyperlink ref="H85" r:id="rId333"/>
-    <hyperlink ref="M85" r:id="rId334" location="geoid=0500000US39073"/>
+    <hyperlink ref="M85" r:id="rId334" location="geoid=0500000US39049"/>
     <hyperlink ref="N85" r:id="rId335"/>
     <hyperlink ref="O85" r:id="rId336"/>
     <hyperlink ref="H86" r:id="rId337"/>
-    <hyperlink ref="M86" r:id="rId338" location="geoid=0500000US39083"/>
+    <hyperlink ref="M86" r:id="rId338" location="geoid=0500000US39073"/>
     <hyperlink ref="N86" r:id="rId339"/>
     <hyperlink ref="O86" r:id="rId340"/>
     <hyperlink ref="H87" r:id="rId341"/>
-    <hyperlink ref="M87" r:id="rId342" location="geoid=0500000US39089"/>
+    <hyperlink ref="M87" r:id="rId342" location="geoid=0500000US39083"/>
     <hyperlink ref="N87" r:id="rId343"/>
     <hyperlink ref="O87" r:id="rId344"/>
     <hyperlink ref="H88" r:id="rId345"/>
-    <hyperlink ref="M88" r:id="rId346" location="geoid=0500000US39091"/>
+    <hyperlink ref="M88" r:id="rId346" location="geoid=0500000US39089"/>
     <hyperlink ref="N88" r:id="rId347"/>
     <hyperlink ref="O88" r:id="rId348"/>
     <hyperlink ref="H89" r:id="rId349"/>
-    <hyperlink ref="M89" r:id="rId350" location="geoid=0500000US39097"/>
+    <hyperlink ref="M89" r:id="rId350" location="geoid=0500000US39091"/>
     <hyperlink ref="N89" r:id="rId351"/>
     <hyperlink ref="O89" r:id="rId352"/>
     <hyperlink ref="H90" r:id="rId353"/>
-    <hyperlink ref="M90" r:id="rId354" location="geoid=0500000US39101"/>
+    <hyperlink ref="M90" r:id="rId354" location="geoid=0500000US39097"/>
     <hyperlink ref="N90" r:id="rId355"/>
     <hyperlink ref="O90" r:id="rId356"/>
     <hyperlink ref="H91" r:id="rId357"/>
-    <hyperlink ref="M91" r:id="rId358" location="geoid=0500000US39117"/>
+    <hyperlink ref="M91" r:id="rId358" location="geoid=0500000US39101"/>
     <hyperlink ref="N91" r:id="rId359"/>
     <hyperlink ref="O91" r:id="rId360"/>
     <hyperlink ref="H92" r:id="rId361"/>
-    <hyperlink ref="M92" r:id="rId362" location="geoid=0500000US39127"/>
+    <hyperlink ref="M92" r:id="rId362" location="geoid=0500000US39117"/>
     <hyperlink ref="N92" r:id="rId363"/>
     <hyperlink ref="O92" r:id="rId364"/>
     <hyperlink ref="H93" r:id="rId365"/>
-    <hyperlink ref="M93" r:id="rId366" location="geoid=0500000US39129"/>
+    <hyperlink ref="M93" r:id="rId366" location="geoid=0500000US39127"/>
     <hyperlink ref="N93" r:id="rId367"/>
     <hyperlink ref="O93" r:id="rId368"/>
     <hyperlink ref="H94" r:id="rId369"/>
-    <hyperlink ref="M94" r:id="rId370" location="geoid=0500000US39141"/>
+    <hyperlink ref="M94" r:id="rId370" location="geoid=0500000US39129"/>
     <hyperlink ref="N94" r:id="rId371"/>
     <hyperlink ref="O94" r:id="rId372"/>
     <hyperlink ref="H95" r:id="rId373"/>
-    <hyperlink ref="M95" r:id="rId374" location="geoid=0500000US39159"/>
+    <hyperlink ref="M95" r:id="rId374" location="geoid=0500000US39141"/>
     <hyperlink ref="N95" r:id="rId375"/>
     <hyperlink ref="O95" r:id="rId376"/>
     <hyperlink ref="H96" r:id="rId377"/>
-    <hyperlink ref="M96" r:id="rId378" location="geoid=M010000US001"/>
+    <hyperlink ref="M96" r:id="rId378" location="geoid=0500000US39159"/>
     <hyperlink ref="N96" r:id="rId379"/>
     <hyperlink ref="O96" r:id="rId380"/>
     <hyperlink ref="H97" r:id="rId381"/>
-    <hyperlink ref="M97" r:id="rId382" location="geoid=M100000US3903758"/>
+    <hyperlink ref="M97" r:id="rId382" location="geoid=M010000US001"/>
     <hyperlink ref="N97" r:id="rId383"/>
     <hyperlink ref="O97" r:id="rId384"/>
     <hyperlink ref="H98" r:id="rId385"/>
-    <hyperlink ref="M98" r:id="rId386" location="geoid=M100000US390458020699999"/>
+    <hyperlink ref="M98" r:id="rId386" location="geoid=M100000US3903758"/>
     <hyperlink ref="N98" r:id="rId387"/>
     <hyperlink ref="O98" r:id="rId388"/>
     <hyperlink ref="H99" r:id="rId389"/>
-    <hyperlink ref="M99" r:id="rId390" location="geoid=M100000US390490692299999"/>
+    <hyperlink ref="M99" r:id="rId390" location="geoid=M100000US390458020699999"/>
     <hyperlink ref="N99" r:id="rId391"/>
     <hyperlink ref="O99" r:id="rId392"/>
     <hyperlink ref="H100" r:id="rId393"/>
-    <hyperlink ref="M100" r:id="rId394" location="geoid=M100000US390490944299999"/>
+    <hyperlink ref="M100" r:id="rId394" location="geoid=M100000US390490692299999"/>
     <hyperlink ref="N100" r:id="rId395"/>
     <hyperlink ref="O100" r:id="rId396"/>
     <hyperlink ref="H101" r:id="rId397"/>
-    <hyperlink ref="M101" r:id="rId398" location="geoid=M100000US390491611299999"/>
+    <hyperlink ref="M101" r:id="rId398" location="geoid=M100000US390490944299999"/>
     <hyperlink ref="N101" r:id="rId399"/>
     <hyperlink ref="O101" r:id="rId400"/>
     <hyperlink ref="H102" r:id="rId401"/>
-    <hyperlink ref="M102" r:id="rId402" location="geoid=M100000US390492828099999"/>
+    <hyperlink ref="M102" r:id="rId402" location="geoid=M100000US390491611299999"/>
     <hyperlink ref="N102" r:id="rId403"/>
     <hyperlink ref="O102" r:id="rId404"/>
     <hyperlink ref="H103" r:id="rId405"/>
-    <hyperlink ref="M103" r:id="rId406" location="geoid=M100000US390493777299999"/>
+    <hyperlink ref="M103" r:id="rId406" location="geoid=M100000US390492828099999"/>
     <hyperlink ref="N103" r:id="rId407"/>
     <hyperlink ref="O103" r:id="rId408"/>
     <hyperlink ref="H104" r:id="rId409"/>
-    <hyperlink ref="M104" r:id="rId410" location="geoid=M100000US390493861299999"/>
+    <hyperlink ref="M104" r:id="rId410" location="geoid=M100000US390493777299999"/>
     <hyperlink ref="N104" r:id="rId411"/>
     <hyperlink ref="O104" r:id="rId412"/>
     <hyperlink ref="H105" r:id="rId413"/>
-    <hyperlink ref="M105" r:id="rId414" location="geoid=M100000US390494641099999"/>
+    <hyperlink ref="M105" r:id="rId414" location="geoid=M100000US390493861299999"/>
     <hyperlink ref="N105" r:id="rId415"/>
     <hyperlink ref="O105" r:id="rId416"/>
     <hyperlink ref="H106" r:id="rId417"/>
-    <hyperlink ref="M106" r:id="rId418" location="geoid=M100000US390495006499999"/>
+    <hyperlink ref="M106" r:id="rId418" location="geoid=M100000US390494641099999"/>
     <hyperlink ref="N106" r:id="rId419"/>
     <hyperlink ref="O106" r:id="rId420"/>
     <hyperlink ref="H107" r:id="rId421"/>
-    <hyperlink ref="M107" r:id="rId422" location="geoid=M100000US390496184099999"/>
+    <hyperlink ref="M107" r:id="rId422" location="geoid=M100000US390495006499999"/>
     <hyperlink ref="N107" r:id="rId423"/>
     <hyperlink ref="O107" r:id="rId424"/>
     <hyperlink ref="H108" r:id="rId425"/>
-    <hyperlink ref="M108" r:id="rId426" location="geoid=M100000US390496297499999"/>
+    <hyperlink ref="M108" r:id="rId426" location="geoid=M100000US390496184099999"/>
     <hyperlink ref="N108" r:id="rId427"/>
     <hyperlink ref="O108" r:id="rId428"/>
     <hyperlink ref="H109" r:id="rId429"/>
-    <hyperlink ref="M109" r:id="rId430" location="geoid=M100000US390496457099999"/>
+    <hyperlink ref="M109" r:id="rId430" location="geoid=M100000US390496297499999"/>
     <hyperlink ref="N109" r:id="rId431"/>
     <hyperlink ref="O109" r:id="rId432"/>
     <hyperlink ref="H110" r:id="rId433"/>
-    <hyperlink ref="M110" r:id="rId434" location="geoid=M100000US390497771499999"/>
+    <hyperlink ref="M110" r:id="rId434" location="geoid=M100000US390496457099999"/>
     <hyperlink ref="N110" r:id="rId435"/>
     <hyperlink ref="O110" r:id="rId436"/>
     <hyperlink ref="H111" r:id="rId437"/>
-    <hyperlink ref="M111" r:id="rId438" location="geoid=M100000US390498124299999"/>
+    <hyperlink ref="M111" r:id="rId438" location="geoid=M100000US390497771499999"/>
     <hyperlink ref="N111" r:id="rId439"/>
     <hyperlink ref="O111" r:id="rId440"/>
     <hyperlink ref="H112" r:id="rId441"/>
-    <hyperlink ref="M112" r:id="rId442" location="geoid=M100000US3905130"/>
+    <hyperlink ref="M112" r:id="rId442" location="geoid=M100000US390498124299999"/>
     <hyperlink ref="N112" r:id="rId443"/>
     <hyperlink ref="O112" r:id="rId444"/>
     <hyperlink ref="H113" r:id="rId445"/>
-    <hyperlink ref="M113" r:id="rId446" location="geoid=M100000US3906278"/>
+    <hyperlink ref="M113" r:id="rId446" location="geoid=M100000US3905130"/>
     <hyperlink ref="N113" r:id="rId447"/>
     <hyperlink ref="O113" r:id="rId448"/>
     <hyperlink ref="H114" r:id="rId449"/>
-    <hyperlink ref="M114" r:id="rId450" location="geoid=M100000US390892569099999"/>
+    <hyperlink ref="M114" r:id="rId450" location="geoid=M100000US3906278"/>
     <hyperlink ref="N114" r:id="rId451"/>
     <hyperlink ref="O114" r:id="rId452"/>
     <hyperlink ref="H115" r:id="rId453"/>
-    <hyperlink ref="M115" r:id="rId454" location="geoid=M100000US390893141699999"/>
+    <hyperlink ref="M115" r:id="rId454" location="geoid=M100000US390892569099999"/>
     <hyperlink ref="N115" r:id="rId455"/>
     <hyperlink ref="O115" r:id="rId456"/>
     <hyperlink ref="H116" r:id="rId457"/>
-    <hyperlink ref="M116" r:id="rId458" location="geoid=M100000US3909890"/>
+    <hyperlink ref="M116" r:id="rId458" location="geoid=M100000US390893141699999"/>
     <hyperlink ref="N116" r:id="rId459"/>
     <hyperlink ref="O116" r:id="rId460"/>
     <hyperlink ref="H117" r:id="rId461"/>
-    <hyperlink ref="M117" r:id="rId462" location="geoid=M100000US3914184"/>
+    <hyperlink ref="M117" r:id="rId462" location="geoid=M100000US3909890"/>
     <hyperlink ref="N117" r:id="rId463"/>
     <hyperlink ref="O117" r:id="rId464"/>
     <hyperlink ref="H118" r:id="rId465"/>
-    <hyperlink ref="M118" r:id="rId466" location="geoid=M100000US3915070"/>
+    <hyperlink ref="M118" r:id="rId466" location="geoid=M100000US3914184"/>
     <hyperlink ref="N118" r:id="rId467"/>
     <hyperlink ref="O118" r:id="rId468"/>
     <hyperlink ref="H119" r:id="rId469"/>
-    <hyperlink ref="M119" r:id="rId470" location="geoid=M100000US391593904699999"/>
+    <hyperlink ref="M119" r:id="rId470" location="geoid=M100000US3915070"/>
     <hyperlink ref="N119" r:id="rId471"/>
     <hyperlink ref="O119" r:id="rId472"/>
     <hyperlink ref="H120" r:id="rId473"/>
-    <hyperlink ref="M120" r:id="rId474" location="geoid=M100000US3918000"/>
+    <hyperlink ref="M120" r:id="rId474" location="geoid=M100000US391593904699999"/>
     <hyperlink ref="N120" r:id="rId475"/>
     <hyperlink ref="O120" r:id="rId476"/>
     <hyperlink ref="H121" r:id="rId477"/>
-    <hyperlink ref="M121" r:id="rId478" location="geoid=M100000US3921434"/>
+    <hyperlink ref="M121" r:id="rId478" location="geoid=M100000US3918000"/>
     <hyperlink ref="N121" r:id="rId479"/>
     <hyperlink ref="O121" r:id="rId480"/>
     <hyperlink ref="H122" r:id="rId481"/>
-    <hyperlink ref="M122" r:id="rId482" location="geoid=M100000US3922694"/>
+    <hyperlink ref="M122" r:id="rId482" location="geoid=M100000US3921434"/>
     <hyperlink ref="N122" r:id="rId483"/>
     <hyperlink ref="O122" r:id="rId484"/>
     <hyperlink ref="H123" r:id="rId485"/>
-    <hyperlink ref="M123" r:id="rId486" location="geoid=M100000US3929106"/>
+    <hyperlink ref="M123" r:id="rId486" location="geoid=M100000US3922694"/>
     <hyperlink ref="N123" r:id="rId487"/>
     <hyperlink ref="O123" r:id="rId488"/>
     <hyperlink ref="H124" r:id="rId489"/>
-    <hyperlink ref="M124" r:id="rId490" location="geoid=M100000US3929148"/>
+    <hyperlink ref="M124" r:id="rId490" location="geoid=M100000US3929106"/>
     <hyperlink ref="N124" r:id="rId491"/>
     <hyperlink ref="O124" r:id="rId492"/>
     <hyperlink ref="H125" r:id="rId493"/>
-    <hyperlink ref="M125" r:id="rId494" location="geoid=M100000US3929246"/>
+    <hyperlink ref="M125" r:id="rId494" location="geoid=M100000US3929148"/>
     <hyperlink ref="N125" r:id="rId495"/>
     <hyperlink ref="O125" r:id="rId496"/>
     <hyperlink ref="H126" r:id="rId497"/>
-    <hyperlink ref="M126" r:id="rId498" location="geoid=M100000US3931304"/>
+    <hyperlink ref="M126" r:id="rId498" location="geoid=M100000US3929246"/>
     <hyperlink ref="N126" r:id="rId499"/>
     <hyperlink ref="O126" r:id="rId500"/>
     <hyperlink ref="H127" r:id="rId501"/>
-    <hyperlink ref="M127" r:id="rId502" location="geoid=M100000US3931402"/>
+    <hyperlink ref="M127" r:id="rId502" location="geoid=M100000US3931304"/>
     <hyperlink ref="N127" r:id="rId503"/>
     <hyperlink ref="O127" r:id="rId504"/>
     <hyperlink ref="H128" r:id="rId505"/>
-    <hyperlink ref="M128" r:id="rId506" location="geoid=M100000US3932592"/>
+    <hyperlink ref="M128" r:id="rId506" location="geoid=M100000US3931402"/>
     <hyperlink ref="N128" r:id="rId507"/>
     <hyperlink ref="O128" r:id="rId508"/>
     <hyperlink ref="H129" r:id="rId509"/>
-    <hyperlink ref="M129" r:id="rId510" location="geoid=M100000US3932606"/>
+    <hyperlink ref="M129" r:id="rId510" location="geoid=M100000US3932592"/>
     <hyperlink ref="N129" r:id="rId511"/>
     <hyperlink ref="O129" r:id="rId512"/>
     <hyperlink ref="H130" r:id="rId513"/>
-    <hyperlink ref="M130" r:id="rId514" location="geoid=M100000US3934748"/>
+    <hyperlink ref="M130" r:id="rId514" location="geoid=M100000US3932606"/>
     <hyperlink ref="N130" r:id="rId515"/>
     <hyperlink ref="O130" r:id="rId516"/>
     <hyperlink ref="H131" r:id="rId517"/>
-    <hyperlink ref="M131" r:id="rId518" location="geoid=M100000US3934790"/>
+    <hyperlink ref="M131" r:id="rId518" location="geoid=M100000US3934748"/>
     <hyperlink ref="N131" r:id="rId519"/>
     <hyperlink ref="O131" r:id="rId520"/>
     <hyperlink ref="H132" r:id="rId521"/>
-    <hyperlink ref="M132" r:id="rId522" location="geoid=M100000US3935476"/>
+    <hyperlink ref="M132" r:id="rId522" location="geoid=M100000US3934790"/>
     <hyperlink ref="N132" r:id="rId523"/>
     <hyperlink ref="O132" r:id="rId524"/>
     <hyperlink ref="H133" r:id="rId525"/>
-    <hyperlink ref="M133" r:id="rId526" location="geoid=M100000US3939340"/>
+    <hyperlink ref="M133" r:id="rId526" location="geoid=M100000US3935476"/>
     <hyperlink ref="N133" r:id="rId527"/>
     <hyperlink ref="O133" r:id="rId528"/>
     <hyperlink ref="H134" r:id="rId529"/>
-    <hyperlink ref="M134" r:id="rId530" location="geoid=M100000US3941720"/>
+    <hyperlink ref="M134" r:id="rId530" location="geoid=M100000US3939340"/>
     <hyperlink ref="N134" r:id="rId531"/>
     <hyperlink ref="O134" r:id="rId532"/>
     <hyperlink ref="H135" r:id="rId533"/>
-    <hyperlink ref="M135" r:id="rId534" location="geoid=M100000US3944674"/>
+    <hyperlink ref="M135" r:id="rId534" location="geoid=M100000US3941720"/>
     <hyperlink ref="N135" r:id="rId535"/>
     <hyperlink ref="O135" r:id="rId536"/>
     <hyperlink ref="H136" r:id="rId537"/>
-    <hyperlink ref="M136" r:id="rId538" location="geoid=M100000US3947474"/>
+    <hyperlink ref="M136" r:id="rId538" location="geoid=M100000US3944674"/>
     <hyperlink ref="N136" r:id="rId539"/>
     <hyperlink ref="O136" r:id="rId540"/>
     <hyperlink ref="H137" r:id="rId541"/>
-    <hyperlink ref="M137" r:id="rId542" location="geoid=M100000US3947754"/>
+    <hyperlink ref="M137" r:id="rId542" location="geoid=M100000US3947474"/>
     <hyperlink ref="N137" r:id="rId543"/>
     <hyperlink ref="O137" r:id="rId544"/>
     <hyperlink ref="H138" r:id="rId545"/>
-    <hyperlink ref="M138" r:id="rId546" location="geoid=M100000US3948160"/>
+    <hyperlink ref="M138" r:id="rId546" location="geoid=M100000US3947754"/>
     <hyperlink ref="N138" r:id="rId547"/>
     <hyperlink ref="O138" r:id="rId548"/>
     <hyperlink ref="H139" r:id="rId549"/>
-    <hyperlink ref="M139" r:id="rId550" location="geoid=M100000US3950862"/>
+    <hyperlink ref="M139" r:id="rId550" location="geoid=M100000US3948160"/>
     <hyperlink ref="N139" r:id="rId551"/>
     <hyperlink ref="O139" r:id="rId552"/>
     <hyperlink ref="H140" r:id="rId553"/>
-    <hyperlink ref="M140" r:id="rId554" location="geoid=M100000US3953046"/>
+    <hyperlink ref="M140" r:id="rId554" location="geoid=M100000US3950862"/>
     <hyperlink ref="N140" r:id="rId555"/>
     <hyperlink ref="O140" r:id="rId556"/>
     <hyperlink ref="H141" r:id="rId557"/>
-    <hyperlink ref="M141" r:id="rId558" location="geoid=M100000US3953102"/>
+    <hyperlink ref="M141" r:id="rId558" location="geoid=M100000US3953046"/>
     <hyperlink ref="N141" r:id="rId559"/>
     <hyperlink ref="O141" r:id="rId560"/>
     <hyperlink ref="H142" r:id="rId561"/>
-    <hyperlink ref="M142" r:id="rId562" location="geoid=M100000US3953970"/>
+    <hyperlink ref="M142" r:id="rId562" location="geoid=M100000US3953102"/>
     <hyperlink ref="N142" r:id="rId563"/>
     <hyperlink ref="O142" r:id="rId564"/>
     <hyperlink ref="H143" r:id="rId565"/>
-    <hyperlink ref="M143" r:id="rId566" location="geoid=M100000US3954040"/>
+    <hyperlink ref="M143" r:id="rId566" location="geoid=M100000US3953970"/>
     <hyperlink ref="N143" r:id="rId567"/>
     <hyperlink ref="O143" r:id="rId568"/>
     <hyperlink ref="H144" r:id="rId569"/>
-    <hyperlink ref="M144" r:id="rId570" location="geoid=M100000US3954866"/>
+    <hyperlink ref="M144" r:id="rId570" location="geoid=M100000US3954040"/>
     <hyperlink ref="N144" r:id="rId571"/>
     <hyperlink ref="O144" r:id="rId572"/>
     <hyperlink ref="H145" r:id="rId573"/>
-    <hyperlink ref="M145" r:id="rId574" location="geoid=M100000US3957862"/>
+    <hyperlink ref="M145" r:id="rId574" location="geoid=M100000US3954866"/>
     <hyperlink ref="N145" r:id="rId575"/>
     <hyperlink ref="O145" r:id="rId576"/>
     <hyperlink ref="H146" r:id="rId577"/>
-    <hyperlink ref="M146" r:id="rId578" location="geoid=M100000US3961112"/>
+    <hyperlink ref="M146" r:id="rId578" location="geoid=M100000US3957862"/>
     <hyperlink ref="N146" r:id="rId579"/>
     <hyperlink ref="O146" r:id="rId580"/>
     <hyperlink ref="H147" r:id="rId581"/>
-    <hyperlink ref="M147" r:id="rId582" location="geoid=M100000US3962498"/>
+    <hyperlink ref="M147" r:id="rId582" location="geoid=M100000US3961112"/>
     <hyperlink ref="N147" r:id="rId583"/>
     <hyperlink ref="O147" r:id="rId584"/>
     <hyperlink ref="H148" r:id="rId585"/>
-    <hyperlink ref="M148" r:id="rId586" location="geoid=M100000US3963030"/>
+    <hyperlink ref="M148" r:id="rId586" location="geoid=M100000US3962498"/>
     <hyperlink ref="N148" r:id="rId587"/>
     <hyperlink ref="O148" r:id="rId588"/>
     <hyperlink ref="H149" r:id="rId589"/>
-    <hyperlink ref="M149" r:id="rId590" location="geoid=M100000US3964486"/>
+    <hyperlink ref="M149" r:id="rId590" location="geoid=M100000US3963030"/>
     <hyperlink ref="N149" r:id="rId591"/>
     <hyperlink ref="O149" r:id="rId592"/>
     <hyperlink ref="H150" r:id="rId593"/>
-    <hyperlink ref="M150" r:id="rId594" location="geoid=M100000US3966390"/>
+    <hyperlink ref="M150" r:id="rId594" location="geoid=M100000US3964486"/>
     <hyperlink ref="N150" r:id="rId595"/>
     <hyperlink ref="O150" r:id="rId596"/>
     <hyperlink ref="H151" r:id="rId597"/>
-    <hyperlink ref="M151" r:id="rId598" location="geoid=M100000US3967440"/>
+    <hyperlink ref="M151" r:id="rId598" location="geoid=M100000US3966390"/>
     <hyperlink ref="N151" r:id="rId599"/>
     <hyperlink ref="O151" r:id="rId600"/>
     <hyperlink ref="H152" r:id="rId601"/>
-    <hyperlink ref="M152" r:id="rId602" location="geoid=M100000US3971976"/>
+    <hyperlink ref="M152" r:id="rId602" location="geoid=M100000US3967440"/>
     <hyperlink ref="N152" r:id="rId603"/>
     <hyperlink ref="O152" r:id="rId604"/>
     <hyperlink ref="H153" r:id="rId605"/>
-    <hyperlink ref="M153" r:id="rId606" location="geoid=M100000US3972977"/>
+    <hyperlink ref="M153" r:id="rId606" location="geoid=M100000US3971976"/>
     <hyperlink ref="N153" r:id="rId607"/>
     <hyperlink ref="O153" r:id="rId608"/>
     <hyperlink ref="H154" r:id="rId609"/>
-    <hyperlink ref="M154" r:id="rId610" location="geoid=M100000US3975602"/>
+    <hyperlink ref="M154" r:id="rId610" location="geoid=M100000US3972977"/>
     <hyperlink ref="N154" r:id="rId611"/>
     <hyperlink ref="O154" r:id="rId612"/>
     <hyperlink ref="H155" r:id="rId613"/>
-    <hyperlink ref="M155" r:id="rId614" location="geoid=M100000US3979002"/>
+    <hyperlink ref="M155" r:id="rId614" location="geoid=M100000US3975602"/>
     <hyperlink ref="N155" r:id="rId615"/>
     <hyperlink ref="O155" r:id="rId616"/>
     <hyperlink ref="H156" r:id="rId617"/>
-    <hyperlink ref="M156" r:id="rId618" location="geoid=M100000US3979100"/>
+    <hyperlink ref="M156" r:id="rId618" location="geoid=M100000US3979002"/>
     <hyperlink ref="N156" r:id="rId619"/>
     <hyperlink ref="O156" r:id="rId620"/>
     <hyperlink ref="H157" r:id="rId621"/>
-    <hyperlink ref="M157" r:id="rId622" location="geoid=M100000US3983580"/>
+    <hyperlink ref="M157" r:id="rId622" location="geoid=M100000US3979100"/>
     <hyperlink ref="N157" r:id="rId623"/>
     <hyperlink ref="O157" r:id="rId624"/>
     <hyperlink ref="H158" r:id="rId625"/>
-    <hyperlink ref="M158" r:id="rId626" location="geoid=M100000US3984742"/>
+    <hyperlink ref="M158" r:id="rId626" location="geoid=M100000US3983342"/>
     <hyperlink ref="N158" r:id="rId627"/>
     <hyperlink ref="O158" r:id="rId628"/>
     <hyperlink ref="H159" r:id="rId629"/>
-    <hyperlink ref="M159" r:id="rId630" location="geoid=M100000US3986604"/>
+    <hyperlink ref="M159" r:id="rId630" location="geoid=M100000US3983580"/>
     <hyperlink ref="N159" r:id="rId631"/>
     <hyperlink ref="O159" r:id="rId632"/>
+    <hyperlink ref="H160" r:id="rId633"/>
+    <hyperlink ref="M160" r:id="rId634" location="geoid=M100000US3984742"/>
+    <hyperlink ref="N160" r:id="rId635"/>
+    <hyperlink ref="O160" r:id="rId636"/>
+    <hyperlink ref="H161" r:id="rId637"/>
+    <hyperlink ref="M161" r:id="rId638" location="geoid=M100000US3986604"/>
+    <hyperlink ref="N161" r:id="rId639"/>
+    <hyperlink ref="O161" r:id="rId640"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
